--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-14).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-14).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-174</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>R$ 601.254,27</t>
-  </si>
-  <si>
-    <t>R$ 3.267,69
-R$ 3.339,21</t>
-  </si>
-  <si>
-    <t>8.6%
-11.0%</t>
+175</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>R$ 604.009,99</t>
+  </si>
+  <si>
+    <t>R$ 3.264,92
+R$ 3.335,88</t>
+  </si>
+  <si>
+    <t>8.8%
+11.1%</t>
   </si>
   <si>
     <t>37.4</t>
   </si>
   <si>
-    <t>2.9%</t>
-  </si>
-  <si>
-    <t>(4.9%)</t>
-  </si>
-  <si>
-    <t>(52.0%)</t>
+    <t>3.1%</t>
+  </si>
+  <si>
+    <t>(4.8%)</t>
+  </si>
+  <si>
+    <t>(51.9%)</t>
   </si>
   <si>
     <t>4.3%</t>
@@ -956,7 +956,7 @@
     <t>10.8%</t>
   </si>
   <si>
-    <t>4.8</t>
+    <t>4.9</t>
   </si>
   <si>
     <t>7.7</t>
@@ -968,13 +968,13 @@
     <t>19.1</t>
   </si>
   <si>
-    <t>71.8%</t>
+    <t>71.9%</t>
   </si>
   <si>
     <t>-R$ 22.938,42</t>
   </si>
   <si>
-    <t>2.95</t>
+    <t>2.94</t>
   </si>
   <si>
     <t>3.52</t>
@@ -6650,7 +6650,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>44</v>
@@ -6686,25 +6686,61 @@
       <c t="s" r="N42" s="4">
         <v>52</v>
       </c>
-      <c r="O42" s="5"/>
-      <c r="P42" s="5"/>
-      <c r="Q42" s="6"/>
-      <c r="R42" s="7"/>
-      <c r="S42" s="6"/>
-      <c r="T42" s="6"/>
-      <c r="U42" s="6"/>
-      <c r="V42" s="6"/>
-      <c r="W42" s="6"/>
-      <c r="X42" s="8"/>
-      <c r="Y42" s="6"/>
-      <c r="Z42" s="6"/>
-      <c r="AA42" s="8"/>
-      <c r="AB42" s="8"/>
-      <c r="AC42" s="8"/>
-      <c r="AD42" s="8"/>
-      <c r="AE42" s="6"/>
+      <c r="O42" s="5">
+        <v>2755.7199999999998</v>
+      </c>
+      <c r="P42" s="5">
+        <v>2755.7199999999998</v>
+      </c>
+      <c r="Q42" s="6">
+        <v>0.67087256786335758</v>
+      </c>
+      <c r="R42" s="7">
+        <v>34</v>
+      </c>
+      <c r="S42" s="6">
+        <v>1</v>
+      </c>
+      <c r="T42" s="6">
+        <v>0.1591194678704658</v>
+      </c>
+      <c r="U42" s="6">
+        <v>-0.16250609641037553</v>
+      </c>
+      <c r="V42" s="6">
+        <v>0.057996095394307119</v>
+      </c>
+      <c r="W42" s="6">
+        <v>0.0057810662912052028</v>
+      </c>
+      <c r="X42" s="8">
+        <v>24.384720833333333</v>
+      </c>
+      <c r="Y42" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="Z42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="8">
+        <v>5.2371428571428575</v>
+      </c>
+      <c r="AB42" s="8">
+        <v>6.4022727272727273</v>
+      </c>
+      <c r="AC42" s="8">
+        <v>12.275188</v>
+      </c>
+      <c r="AD42" s="8">
+        <v>18.518054166666666</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>0.83333333333333337</v>
+      </c>
       <c r="AF42" s="9"/>
-      <c r="AG42" s="5"/>
+      <c r="AG42" s="5">
+        <v>0</v>
+      </c>
       <c r="AH42" s="10">
         <v>3</v>
       </c>
@@ -20735,7 +20771,7 @@
         <v>-1149.8</v>
       </c>
       <c r="AH153" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI153" s="11"/>
       <c r="AJ153" s="13">

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-14).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-14).xlsx
@@ -912,21 +912,21 @@
   </si>
   <si>
     <t>214
-175</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>R$ 604.009,99</t>
-  </si>
-  <si>
-    <t>R$ 3.264,92
-R$ 3.335,88</t>
-  </si>
-  <si>
-    <t>8.8%
-11.1%</t>
+176</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>R$ 607.203,18</t>
+  </si>
+  <si>
+    <t>R$ 3.264,53
+R$ 3.335,07</t>
+  </si>
+  <si>
+    <t>8.9%
+11.2%</t>
   </si>
   <si>
     <t>37.4</t>
@@ -935,10 +935,10 @@
     <t>3.1%</t>
   </si>
   <si>
-    <t>(4.8%)</t>
-  </si>
-  <si>
-    <t>(51.9%)</t>
+    <t>(4.7%)</t>
+  </si>
+  <si>
+    <t>(51.7%)</t>
   </si>
   <si>
     <t>4.3%</t>
@@ -947,16 +947,16 @@
     <t>(0.1%)</t>
   </si>
   <si>
-    <t>27.6</t>
-  </si>
-  <si>
-    <t>69.5%</t>
-  </si>
-  <si>
-    <t>10.8%</t>
-  </si>
-  <si>
-    <t>4.9</t>
+    <t>27.5</t>
+  </si>
+  <si>
+    <t>69.2%</t>
+  </si>
+  <si>
+    <t>10.7%</t>
+  </si>
+  <si>
+    <t>4.8</t>
   </si>
   <si>
     <t>7.7</t>
@@ -968,13 +968,13 @@
     <t>19.1</t>
   </si>
   <si>
-    <t>71.9%</t>
+    <t>72.0%</t>
   </si>
   <si>
     <t>-R$ 22.938,42</t>
   </si>
   <si>
-    <t>2.94</t>
+    <t>2.95</t>
   </si>
   <si>
     <t>3.52</t>
@@ -8698,7 +8698,7 @@
         <v>19618</v>
       </c>
       <c r="B58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C58" s="4">
         <v>44</v>
@@ -8734,25 +8734,61 @@
       <c t="s" r="N58" s="4">
         <v>52</v>
       </c>
-      <c r="O58" s="5"/>
-      <c r="P58" s="5"/>
-      <c r="Q58" s="6"/>
-      <c r="R58" s="7"/>
-      <c r="S58" s="6"/>
-      <c r="T58" s="6"/>
-      <c r="U58" s="6"/>
-      <c r="V58" s="6"/>
-      <c r="W58" s="6"/>
-      <c r="X58" s="8"/>
-      <c r="Y58" s="6"/>
-      <c r="Z58" s="6"/>
-      <c r="AA58" s="8"/>
-      <c r="AB58" s="8"/>
-      <c r="AC58" s="8"/>
-      <c r="AD58" s="8"/>
-      <c r="AE58" s="6"/>
+      <c r="O58" s="5">
+        <v>3193.1900000000001</v>
+      </c>
+      <c r="P58" s="5">
+        <v>3193.1900000000001</v>
+      </c>
+      <c r="Q58" s="6">
+        <v>0.1958438192821621</v>
+      </c>
+      <c r="R58" s="7">
+        <v>37</v>
+      </c>
+      <c r="S58" s="6">
+        <v>-0.026315789473684181</v>
+      </c>
+      <c r="T58" s="6">
+        <v>0.13909353968915097</v>
+      </c>
+      <c r="U58" s="6">
+        <v>-0.22379435611410531</v>
+      </c>
+      <c r="V58" s="6">
+        <v>0.016863074229845391</v>
+      </c>
+      <c r="W58" s="6">
+        <v>-0.0077298876671917423</v>
+      </c>
+      <c r="X58" s="8">
+        <v>24.339705882352941</v>
+      </c>
+      <c r="Y58" s="6">
+        <v>0.41176470588235292</v>
+      </c>
+      <c r="Z58" s="6">
+        <v>0.029411764705882353</v>
+      </c>
+      <c r="AA58" s="8">
+        <v>3.3421052631578947</v>
+      </c>
+      <c r="AB58" s="8">
+        <v>7.3916676470588234</v>
+      </c>
+      <c r="AC58" s="8">
+        <v>10.641176</v>
+      </c>
+      <c r="AD58" s="8">
+        <v>17.541667647058823</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>0.8529411764705882</v>
+      </c>
       <c r="AF58" s="9"/>
-      <c r="AG58" s="5"/>
+      <c r="AG58" s="5">
+        <v>0</v>
+      </c>
       <c r="AH58" s="10">
         <v>2</v>
       </c>
@@ -15381,7 +15417,9 @@
       <c r="AB111" s="8">
         <v>2.3166666666666669</v>
       </c>
-      <c r="AC111" s="8"/>
+      <c r="AC111" s="8">
+        <v>9.1944429999999997</v>
+      </c>
       <c r="AD111" s="8">
         <v>16.161100000000001</v>
       </c>
@@ -16883,7 +16921,7 @@
         <v>0</v>
       </c>
       <c r="AH123" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI123" s="11"/>
       <c r="AJ123" s="13">
@@ -17276,7 +17314,7 @@
         <v>0</v>
       </c>
       <c r="AH126" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI126" s="11"/>
       <c r="AJ126" s="13">
@@ -18453,7 +18491,7 @@
         <v>-41.899999999999999</v>
       </c>
       <c r="AH135" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI135" s="11"/>
       <c r="AJ135" s="13">
@@ -21983,7 +22021,7 @@
         <v>-923.55999999999995</v>
       </c>
       <c r="AH163" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI163" s="11"/>
       <c r="AJ163" s="13">
@@ -28110,7 +28148,7 @@
       <c r="AF212" s="9"/>
       <c r="AG212" s="5"/>
       <c r="AH212" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI212" s="11"/>
       <c r="AJ212" s="12"/>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-14).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-14).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-176</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>R$ 607.203,18</t>
-  </si>
-  <si>
-    <t>R$ 3.264,53
-R$ 3.335,07</t>
-  </si>
-  <si>
-    <t>8.9%
-11.2%</t>
-  </si>
-  <si>
-    <t>37.4</t>
-  </si>
-  <si>
-    <t>3.1%</t>
-  </si>
-  <si>
-    <t>(4.7%)</t>
-  </si>
-  <si>
-    <t>(51.7%)</t>
+182</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>R$ 625.231,62</t>
+  </si>
+  <si>
+    <t>R$ 3.256,41
+R$ 3.324,18</t>
+  </si>
+  <si>
+    <t>9.3%
+11.6%</t>
+  </si>
+  <si>
+    <t>37.2</t>
+  </si>
+  <si>
+    <t>3.3%</t>
+  </si>
+  <si>
+    <t>(6.9%)</t>
+  </si>
+  <si>
+    <t>(53.5%)</t>
   </si>
   <si>
     <t>4.3%</t>
@@ -950,31 +950,31 @@
     <t>27.5</t>
   </si>
   <si>
-    <t>69.2%</t>
-  </si>
-  <si>
-    <t>10.7%</t>
+    <t>69.7%</t>
+  </si>
+  <si>
+    <t>10.6%</t>
   </si>
   <si>
     <t>4.8</t>
   </si>
   <si>
-    <t>7.7</t>
-  </si>
-  <si>
-    <t>12.6</t>
-  </si>
-  <si>
-    <t>19.1</t>
-  </si>
-  <si>
-    <t>72.0%</t>
+    <t>7.6</t>
+  </si>
+  <si>
+    <t>12.5</t>
+  </si>
+  <si>
+    <t>19.0</t>
+  </si>
+  <si>
+    <t>72.2%</t>
   </si>
   <si>
     <t>-R$ 22.938,42</t>
   </si>
   <si>
-    <t>2.95</t>
+    <t>2.94</t>
   </si>
   <si>
     <t>3.52</t>
@@ -2066,7 +2066,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>44</v>
@@ -2102,25 +2102,61 @@
       <c t="s" r="N6" s="4">
         <v>52</v>
       </c>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="6"/>
-      <c r="AA6" s="8"/>
-      <c r="AB6" s="8"/>
-      <c r="AC6" s="8"/>
-      <c r="AD6" s="8"/>
-      <c r="AE6" s="6"/>
+      <c r="O6" s="5">
+        <v>6205.1000000000004</v>
+      </c>
+      <c r="P6" s="5">
+        <v>6205.1000000000004</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>0.73769490993816644</v>
+      </c>
+      <c r="R6" s="7">
+        <v>68</v>
+      </c>
+      <c r="S6" s="6">
+        <v>0.38775510204081631</v>
+      </c>
+      <c r="T6" s="6">
+        <v>0.28514314032005927</v>
+      </c>
+      <c r="U6" s="6">
+        <v>-0.057605566388938129</v>
+      </c>
+      <c r="V6" s="6">
+        <v>0.022743791397398912</v>
+      </c>
+      <c r="W6" s="6">
+        <v>-0.0065853088588419192</v>
+      </c>
+      <c r="X6" s="8">
+        <v>21.537907843137255</v>
+      </c>
+      <c r="Y6" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="8">
+        <v>5.1141409090909091</v>
+      </c>
+      <c r="AB6" s="8">
+        <v>3.1287588235294117</v>
+      </c>
+      <c r="AC6" s="8">
+        <v>8.1274499999999996</v>
+      </c>
+      <c r="AD6" s="8">
+        <v>15.087907843137254</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>0.94117647058823528</v>
+      </c>
       <c r="AF6" s="9"/>
-      <c r="AG6" s="5"/>
+      <c r="AG6" s="5">
+        <v>0</v>
+      </c>
       <c r="AH6" s="10">
         <v>5</v>
       </c>
@@ -4364,7 +4400,7 @@
         <v>19536</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C24" s="4">
         <v>44</v>
@@ -4400,25 +4436,59 @@
       <c t="s" r="N24" s="4">
         <v>52</v>
       </c>
-      <c r="O24" s="5"/>
-      <c r="P24" s="5"/>
-      <c r="Q24" s="6"/>
-      <c r="R24" s="7"/>
-      <c r="S24" s="6"/>
-      <c r="T24" s="6"/>
-      <c r="U24" s="6"/>
-      <c r="V24" s="6"/>
-      <c r="W24" s="6"/>
-      <c r="X24" s="8"/>
-      <c r="Y24" s="6"/>
-      <c r="Z24" s="6"/>
-      <c r="AA24" s="8"/>
-      <c r="AB24" s="8"/>
+      <c r="O24" s="5">
+        <v>2713.7199999999998</v>
+      </c>
+      <c r="P24" s="5">
+        <v>2713.7199999999998</v>
+      </c>
+      <c r="Q24" s="6">
+        <v>0.308207753642052</v>
+      </c>
+      <c r="R24" s="7">
+        <v>32</v>
+      </c>
+      <c r="S24" s="6">
+        <v>0.032258064516129004</v>
+      </c>
+      <c r="T24" s="6">
+        <v>0</v>
+      </c>
+      <c r="U24" s="6">
+        <v>-0.36725601756997778</v>
+      </c>
+      <c r="V24" s="6">
+        <v>0.10574690830299367</v>
+      </c>
+      <c r="W24" s="6">
+        <v>0.020071156935866634</v>
+      </c>
+      <c r="X24" s="8">
+        <v>27.688890476190473</v>
+      </c>
+      <c r="Y24" s="6">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="Z24" s="6">
+        <v>0.047619047619047616</v>
+      </c>
+      <c r="AA24" s="8">
+        <v>3.0204290322580647</v>
+      </c>
+      <c r="AB24" s="8">
+        <v>9.7595238095238095</v>
+      </c>
       <c r="AC24" s="8"/>
-      <c r="AD24" s="8"/>
-      <c r="AE24" s="6"/>
+      <c r="AD24" s="8">
+        <v>19.833333333333332</v>
+      </c>
+      <c r="AE24" s="6">
+        <v>0.80952380952380953</v>
+      </c>
       <c r="AF24" s="9"/>
-      <c r="AG24" s="5"/>
+      <c r="AG24" s="5">
+        <v>0</v>
+      </c>
       <c r="AH24" s="10">
         <v>2</v>
       </c>
@@ -5686,10 +5756,10 @@
         <v>0.39655172413793105</v>
       </c>
       <c r="T34" s="6">
-        <v>0.30866309370424327</v>
+        <v>-0.37878021232073633</v>
       </c>
       <c r="U34" s="6">
-        <v>-0.0061097844441493987</v>
+        <v>-0.69355309046912894</v>
       </c>
       <c r="V34" s="6">
         <v>0.075112527746247368</v>
@@ -5900,7 +5970,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>44</v>
@@ -5936,25 +6006,61 @@
       <c t="s" r="N36" s="4">
         <v>52</v>
       </c>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="7"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="8"/>
-      <c r="Y36" s="6"/>
-      <c r="Z36" s="6"/>
-      <c r="AA36" s="8"/>
-      <c r="AB36" s="8"/>
-      <c r="AC36" s="8"/>
-      <c r="AD36" s="8"/>
-      <c r="AE36" s="6"/>
+      <c r="O36" s="5">
+        <v>2867.46</v>
+      </c>
+      <c r="P36" s="5">
+        <v>2867.46</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>0.48565359307807898</v>
+      </c>
+      <c r="R36" s="7">
+        <v>35</v>
+      </c>
+      <c r="S36" s="6">
+        <v>0.52173913043478271</v>
+      </c>
+      <c r="T36" s="6">
+        <v>0.32693509238141072</v>
+      </c>
+      <c r="U36" s="6">
+        <v>0.0017204424821967875</v>
+      </c>
+      <c r="V36" s="6">
+        <v>0.093179678182084502</v>
+      </c>
+      <c r="W36" s="6">
+        <v>0.025060157770291476</v>
+      </c>
+      <c r="X36" s="8">
+        <v>23.185416666666669</v>
+      </c>
+      <c r="Y36" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="8">
+        <v>4.9752371428571429</v>
+      </c>
+      <c r="AB36" s="8">
+        <v>3.5270833333333336</v>
+      </c>
+      <c r="AC36" s="8">
+        <v>8.6763879999999993</v>
+      </c>
+      <c r="AD36" s="8">
+        <v>15.629166666666668</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>0.875</v>
+      </c>
       <c r="AF36" s="9"/>
-      <c r="AG36" s="5"/>
+      <c r="AG36" s="5">
+        <v>0</v>
+      </c>
       <c r="AH36" s="10">
         <v>4</v>
       </c>
@@ -7821,7 +7927,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7857,25 +7963,61 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="8"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
-      <c r="AA51" s="8"/>
-      <c r="AB51" s="8"/>
-      <c r="AC51" s="8"/>
-      <c r="AD51" s="8"/>
-      <c r="AE51" s="6"/>
+      <c r="O51" s="5">
+        <v>659.10000000000002</v>
+      </c>
+      <c r="P51" s="5">
+        <v>659.10000000000002</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>0.13583097814848011</v>
+      </c>
+      <c r="R51" s="7">
+        <v>5</v>
+      </c>
+      <c r="S51" s="6">
+        <v>-0.375</v>
+      </c>
+      <c r="T51" s="6">
+        <v>0</v>
+      </c>
+      <c r="U51" s="6">
+        <v>-0.28793809740555304</v>
+      </c>
+      <c r="V51" s="6">
+        <v>0.045999089667728719</v>
+      </c>
+      <c r="W51" s="6">
+        <v>-0.14822030040964951</v>
+      </c>
+      <c r="X51" s="8">
+        <v>46.700000000000003</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z51" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="AA51" s="8">
+        <v>6.6699999999999999</v>
+      </c>
+      <c r="AB51" s="8">
+        <v>22.875</v>
+      </c>
+      <c r="AC51" s="8">
+        <v>30.308333000000001</v>
+      </c>
+      <c r="AD51" s="8">
+        <v>37.225000000000001</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>0</v>
+      </c>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -8777,7 +8919,7 @@
         <v>7.3916676470588234</v>
       </c>
       <c r="AC58" s="8">
-        <v>10.641176</v>
+        <v>10.710352</v>
       </c>
       <c r="AD58" s="8">
         <v>17.541667647058823</v>
@@ -12580,7 +12722,7 @@
         <v>0</v>
       </c>
       <c r="AH88" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI88" s="11"/>
       <c r="AJ88" s="13">
@@ -12619,7 +12761,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>44</v>
@@ -12653,25 +12795,59 @@
       <c t="s" r="N89" s="4">
         <v>52</v>
       </c>
-      <c r="O89" s="5"/>
-      <c r="P89" s="5"/>
-      <c r="Q89" s="6"/>
-      <c r="R89" s="7"/>
-      <c r="S89" s="6"/>
-      <c r="T89" s="6"/>
-      <c r="U89" s="6"/>
-      <c r="V89" s="6"/>
-      <c r="W89" s="6"/>
-      <c r="X89" s="8"/>
-      <c r="Y89" s="6"/>
-      <c r="Z89" s="6"/>
-      <c r="AA89" s="8"/>
-      <c r="AB89" s="8"/>
+      <c r="O89" s="5">
+        <v>2645.1300000000001</v>
+      </c>
+      <c r="P89" s="5">
+        <v>2645.1300000000001</v>
+      </c>
+      <c r="Q89" s="6">
+        <v>-0.18982817237893967</v>
+      </c>
+      <c r="R89" s="7">
+        <v>25</v>
+      </c>
+      <c r="S89" s="6">
+        <v>-0.34210526315789469</v>
+      </c>
+      <c r="T89" s="6">
+        <v>-5.5048204814130113</v>
+      </c>
+      <c r="U89" s="6">
+        <v>-5.8524442276939128</v>
+      </c>
+      <c r="V89" s="6">
+        <v>0.047343608820738486</v>
+      </c>
+      <c r="W89" s="6">
+        <v>0.011368061305115439</v>
+      </c>
+      <c r="X89" s="8">
+        <v>28.598144444444447</v>
+      </c>
+      <c r="Y89" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z89" s="6">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="AA89" s="8">
+        <v>4.5839999999999996</v>
+      </c>
+      <c r="AB89" s="8">
+        <v>6.0222222222222221</v>
+      </c>
       <c r="AC89" s="8"/>
-      <c r="AD89" s="8"/>
-      <c r="AE89" s="6"/>
+      <c r="AD89" s="8">
+        <v>20.092588888888891</v>
+      </c>
+      <c r="AE89" s="6">
+        <v>0.77777777777777779</v>
+      </c>
       <c r="AF89" s="9"/>
-      <c r="AG89" s="5"/>
+      <c r="AG89" s="5">
+        <v>0</v>
+      </c>
       <c r="AH89" s="10">
         <v>2</v>
       </c>
@@ -16659,7 +16835,7 @@
         <v>0</v>
       </c>
       <c r="AH121" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI121" s="11"/>
       <c r="AJ121" s="13">
@@ -18622,7 +18798,7 @@
         <v>-104.7</v>
       </c>
       <c r="AH136" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI136" s="11"/>
       <c r="AJ136" s="13">
@@ -20936,7 +21112,7 @@
         <v>0</v>
       </c>
       <c r="AH154" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI154" s="11"/>
       <c r="AJ154" s="13">
@@ -21330,7 +21506,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>44</v>
@@ -21366,25 +21542,61 @@
       <c t="s" r="N158" s="4">
         <v>52</v>
       </c>
-      <c r="O158" s="5"/>
-      <c r="P158" s="5"/>
-      <c r="Q158" s="6"/>
-      <c r="R158" s="7"/>
-      <c r="S158" s="6"/>
-      <c r="T158" s="6"/>
-      <c r="U158" s="6"/>
-      <c r="V158" s="6"/>
-      <c r="W158" s="6"/>
-      <c r="X158" s="8"/>
-      <c r="Y158" s="6"/>
-      <c r="Z158" s="6"/>
-      <c r="AA158" s="8"/>
-      <c r="AB158" s="8"/>
-      <c r="AC158" s="8"/>
-      <c r="AD158" s="8"/>
-      <c r="AE158" s="6"/>
+      <c r="O158" s="5">
+        <v>2937.9299999999998</v>
+      </c>
+      <c r="P158" s="5">
+        <v>2937.9299999999998</v>
+      </c>
+      <c r="Q158" s="6">
+        <v>0.032555442308368043</v>
+      </c>
+      <c r="R158" s="7">
+        <v>28</v>
+      </c>
+      <c r="S158" s="6">
+        <v>-0.034482758620689613</v>
+      </c>
+      <c r="T158" s="6">
+        <v>0.28529277416412241</v>
+      </c>
+      <c r="U158" s="6">
+        <v>0.0019538246316283914</v>
+      </c>
+      <c r="V158" s="6">
+        <v>0.041647180157457803</v>
+      </c>
+      <c r="W158" s="6">
+        <v>-0.027142750167635035</v>
+      </c>
+      <c r="X158" s="8">
+        <v>30.949999999999999</v>
+      </c>
+      <c r="Y158" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Z158" s="6">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="AA158" s="8">
+        <v>5.0994241379310346</v>
+      </c>
+      <c r="AB158" s="8">
+        <v>7.7950629629629633</v>
+      </c>
+      <c r="AC158" s="8">
+        <v>12.894486000000001</v>
+      </c>
+      <c r="AD158" s="8">
+        <v>19.472024999999999</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>0.5357142857142857</v>
+      </c>
       <c r="AF158" s="9"/>
-      <c r="AG158" s="5"/>
+      <c r="AG158" s="5">
+        <v>0</v>
+      </c>
       <c r="AH158" s="10">
         <v>2</v>
       </c>
@@ -24063,7 +24275,9 @@
       <c r="AB179" s="8">
         <v>1.6878772727272726</v>
       </c>
-      <c r="AC179" s="8"/>
+      <c r="AC179" s="8">
+        <v>6.7340900000000001</v>
+      </c>
       <c r="AD179" s="8">
         <v>13.681059090909089</v>
       </c>
